--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N104_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N104_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.5987556819301</v>
+        <v>11.14729779831364</v>
       </c>
       <c r="D2" t="n">
-        <v>61.38269258641122</v>
+        <v>9.974687545291824</v>
       </c>
       <c r="E2" t="n">
-        <v>20.81124946935389</v>
+        <v>3.381828038770007</v>
       </c>
       <c r="F2" t="n">
-        <v>19.12831200035848</v>
+        <v>3.108350700058252</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.33656638729368</v>
+        <v>1.842192037935223</v>
       </c>
       <c r="D3" t="n">
-        <v>22.60307518934443</v>
+        <v>3.67299971826847</v>
       </c>
       <c r="E3" t="n">
-        <v>20.81124946935389</v>
+        <v>3.381828038770007</v>
       </c>
       <c r="F3" t="n">
-        <v>19.12831200035848</v>
+        <v>3.108350700058252</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.83081167876587</v>
+        <v>5.660006897799454</v>
       </c>
       <c r="D4" t="n">
-        <v>11.50951111905106</v>
+        <v>1.870295556845798</v>
       </c>
       <c r="E4" t="n">
-        <v>20.81124946935389</v>
+        <v>3.381828038770007</v>
       </c>
       <c r="F4" t="n">
-        <v>19.12831200035848</v>
+        <v>3.108350700058252</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.23128855582205</v>
+        <v>4.587584390321084</v>
       </c>
       <c r="D5" t="n">
-        <v>20.74728157791791</v>
+        <v>3.37143325641166</v>
       </c>
       <c r="E5" t="n">
-        <v>20.81124946935389</v>
+        <v>3.381828038770007</v>
       </c>
       <c r="F5" t="n">
-        <v>19.12831200035848</v>
+        <v>3.108350700058252</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
